--- a/data/trans_dic/IP12-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolores o síntomas</t>
+          <t>Menores que limitaron su actividad por dolores o síntomas (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,41; 18,83</t>
+          <t>5,16; 18,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,61; 17,8</t>
+          <t>3,72; 17,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,37; 24,81</t>
+          <t>9,01; 24,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,67; 9,91</t>
+          <t>1,19; 9,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,19; 21,43</t>
+          <t>7,86; 21,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,56; 20,88</t>
+          <t>6,57; 20,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,39; 25,21</t>
+          <t>9,33; 25,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 10,79</t>
+          <t>0,99; 12,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,72; 17,92</t>
+          <t>7,58; 18,16</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,48; 16,5</t>
+          <t>6,57; 16,73</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,15; 22,36</t>
+          <t>10,69; 21,88</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 8,89</t>
+          <t>1,95; 8,81</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,03; 15,34</t>
+          <t>6,14; 15,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,15; 17,08</t>
+          <t>7,59; 17,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,04; 14,66</t>
+          <t>5,46; 15,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,03; 12,93</t>
+          <t>3,25; 12,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,81; 9,5</t>
+          <t>2,32; 9,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,43; 18,57</t>
+          <t>7,94; 18,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,74; 11,92</t>
+          <t>3,78; 11,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,23; 10,6</t>
+          <t>3,03; 11,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,04; 11,04</t>
+          <t>5,25; 11,1</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,64; 15,8</t>
+          <t>9,05; 16,42</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,55; 11,79</t>
+          <t>5,55; 11,77</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,02; 10,38</t>
+          <t>4,22; 10,16</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 11,04</t>
+          <t>1,15; 10,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,33; 19,26</t>
+          <t>6,24; 19,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 8,74</t>
+          <t>0,99; 9,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,41; 19,2</t>
+          <t>5,64; 19,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,78; 9,83</t>
+          <t>1,76; 9,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,13; 17,73</t>
+          <t>5,11; 17,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,82</t>
+          <t>0,0; 6,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,99; 16,42</t>
+          <t>3,89; 16,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 7,63</t>
+          <t>1,93; 7,7</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,07; 16,25</t>
+          <t>7,5; 16,55</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 5,72</t>
+          <t>0,97; 5,34</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,76; 14,45</t>
+          <t>5,83; 14,7</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,66; 14,56</t>
+          <t>4,24; 14,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,27; 18,12</t>
+          <t>5,89; 17,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,87; 20,05</t>
+          <t>7,68; 21,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,22; 13,1</t>
+          <t>2,18; 12,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,75; 17,1</t>
+          <t>5,73; 16,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,28; 13,86</t>
+          <t>3,16; 14,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,09; 19,69</t>
+          <t>7,12; 20,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,44; 20,32</t>
+          <t>3,12; 20,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,15; 13,76</t>
+          <t>5,98; 14,08</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,03; 14,31</t>
+          <t>5,73; 13,76</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,5; 17,68</t>
+          <t>8,46; 17,63</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,56; 13,82</t>
+          <t>3,63; 14,17</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,93</t>
+          <t>0,0; 9,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,85; 31,08</t>
+          <t>10,38; 30,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,85; 20,56</t>
+          <t>4,49; 19,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,14; 19,31</t>
+          <t>4,19; 19,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,49</t>
+          <t>0,0; 7,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,87; 23,45</t>
+          <t>7,22; 23,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,2; 11,63</t>
+          <t>1,18; 10,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,71; 15,6</t>
+          <t>2,55; 14,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 6,31</t>
+          <t>0,72; 6,28</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10,48; 23,7</t>
+          <t>10,07; 23,36</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,46; 12,2</t>
+          <t>3,48; 12,73</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,56; 14,21</t>
+          <t>4,55; 14,03</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,48; 14,2</t>
+          <t>2,47; 14,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,88; 17,71</t>
+          <t>3,95; 17,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,22</t>
+          <t>0,0; 7,2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,97; 17,57</t>
+          <t>4,14; 16,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,04; 11,29</t>
+          <t>2,06; 11,52</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,56; 16,18</t>
+          <t>3,59; 15,27</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,88</t>
+          <t>0,0; 12,06</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,95; 27,1</t>
+          <t>11,32; 27,49</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,07; 10,22</t>
+          <t>2,72; 9,84</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,06; 14,25</t>
+          <t>4,82; 13,58</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,65; 6,18</t>
+          <t>0,64; 6,03</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,29; 19,31</t>
+          <t>9,21; 19,99</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,17; 10,24</t>
+          <t>3,3; 11,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,57; 9,18</t>
+          <t>2,5; 8,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,11; 8,0</t>
+          <t>2,09; 7,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,26; 15,06</t>
+          <t>6,26; 14,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,01; 6,46</t>
+          <t>1,01; 6,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,87; 8,11</t>
+          <t>1,86; 7,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,48; 6,41</t>
+          <t>1,43; 6,59</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,26; 14,07</t>
+          <t>5,41; 14,47</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,81; 6,91</t>
+          <t>2,58; 6,81</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,84; 7,12</t>
+          <t>2,85; 7,2</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,31; 6,27</t>
+          <t>2,35; 6,24</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,57; 13,1</t>
+          <t>6,42; 12,54</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,79; 6,5</t>
+          <t>1,9; 6,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,25; 6,95</t>
+          <t>2,0; 7,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,35; 12,43</t>
+          <t>5,38; 12,07</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,32; 6,08</t>
+          <t>1,48; 6,09</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,78; 12,76</t>
+          <t>5,63; 12,6</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,44; 9,83</t>
+          <t>3,37; 9,48</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,39; 9,41</t>
+          <t>3,46; 9,39</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,99; 9,31</t>
+          <t>3,04; 9,42</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,22; 8,42</t>
+          <t>4,44; 8,81</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3,47; 7,46</t>
+          <t>3,42; 7,37</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5,15; 9,69</t>
+          <t>5,26; 9,53</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,7; 6,69</t>
+          <t>2,8; 6,78</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,04; 8,15</t>
+          <t>5,03; 8,08</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,04; 10,37</t>
+          <t>7,05; 10,49</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,25; 9,63</t>
+          <t>6,33; 9,62</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,52; 8,98</t>
+          <t>5,41; 8,92</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,14; 8,07</t>
+          <t>5,26; 8,01</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,82; 10,27</t>
+          <t>6,8; 10,13</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,06; 8,05</t>
+          <t>5,21; 8,19</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,08; 9,74</t>
+          <t>6,25; 9,82</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,44; 7,59</t>
+          <t>5,45; 7,64</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7,47; 10,0</t>
+          <t>7,37; 9,91</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6,07; 8,36</t>
+          <t>6,23; 8,39</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6,25; 8,73</t>
+          <t>6,28; 8,91</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que limitaron su actividad por dolores o síntomas (tasa de respuesta: 99,99%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>5727</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4945</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9167</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3374</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>7892</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>8227</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>10136</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>3181</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>13620</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>13172</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>19303</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>6555</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2713; 9904</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2135; 9882</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5168; 14285</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>870; 7206</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>4732; 13225</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>4255; 13586</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>6017; 16362</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>786; 9721</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>8545; 20484</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>8031; 20456</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>13021; 26656</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2983; 13450</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>10308</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12138</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9816</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>9519</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>5820</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>13906</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>8007</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>7782</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>16128</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>26043</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>17823</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>17301</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>6239; 16019</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>7943; 18220</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>5673; 16092</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>4126; 16152</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2522; 10407</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>8830; 20063</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>4171; 12891</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>3868; 14286</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>11042; 23336</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>19542; 35446</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>11884; 25205</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>10728; 25849</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>3022</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>8022</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2149</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>6421</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>3138</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>7280</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1355</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>5768</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>6160</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>15302</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3504</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>12189</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>779; 7023</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4255; 13035</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>662; 6017</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>3284; 11310</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1238; 6615</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3643; 12384</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4742</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2611; 10817</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>2656; 10615</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>10453; 23074</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>1326; 7296</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>7314; 18437</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>6451</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8537</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9842</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4084</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>8172</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>6352</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>6845</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>14623</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>14888</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>20148</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>10929</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>3171; 11013</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>4581; 13792</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>5910; 16376</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1529; 8844</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>4533; 12755</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2598; 11539</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>5784; 16455</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2439; 15743</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>9205; 21681</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>9168; 22014</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>13384; 27874</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>5382; 21014</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1333</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>8390</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>4511</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3514</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>6369</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1784</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2806</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>14759</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>6295</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>6319</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4147</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>4557; 13437</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1952; 8623</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1447; 6851</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3370</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>3374; 11009</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>549; 4898</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>1036; 5879</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>625; 5444</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>9126; 21176</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3126; 11434</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>3425; 10553</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>3662</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>5222</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>729</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>4136</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>3082</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>5035</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1766</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>10042</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>6744</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>10257</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2495</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>14179</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>1386; 8016</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>2210; 9832</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3906</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>1914; 7844</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1232; 6880</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>2161; 9197</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 6964</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>6358; 15445</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>3149; 11394</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>5600; 15783</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>717; 6752</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>9426; 20461</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>7572</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>7158</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>5951</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>12233</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>4044</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>6040</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>4847</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>13925</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>11615</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>13197</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>10798</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>26159</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>4243; 14362</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>3462; 12117</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>2866; 10814</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>7796; 18221</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>1375; 8567</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>2707; 11179</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>2066; 9488</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>8435; 22569</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>6825; 17992</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>8112; 20477</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>6602; 17552</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>18018; 35173</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>5803</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>6881</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>13561</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>3990</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>14579</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>10352</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>10280</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>8755</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>20382</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>17233</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>23841</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>12745</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>2995; 10200</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>3301; 11864</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>8797; 19736</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>1950; 8018</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>9237; 20667</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>5771; 16247</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>5911; 16037</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>4772; 14765</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>14282; 28356</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>11485; 24764</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>17603; 31871</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>8087; 19568</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>43878</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>61292</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>55726</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>47272</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>47392</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>63560</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>48482</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>59103</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>91270</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>124852</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>104208</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>106375</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>34289; 55048</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>50187; 74651</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>44576; 67704</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>35978; 59317</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>38030; 57921</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>51223; 76314</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>38826; 61026</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>47607; 74856</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>76515; 107244</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>107969; 145150</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>90269; 121541</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>89665; 127135</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolores o síntomas (tasa de respuesta: 99,99%)</t>
+          <t>Menores que en las últimas 2 semanas limitaron su actividad por dolores o síntomas (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,16; 18,84</t>
+          <t>5,16; 19,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,72; 17,21</t>
+          <t>3,35; 17,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,01; 24,9</t>
+          <t>8,86; 24,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 9,83</t>
+          <t>1,72; 11,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,86; 21,96</t>
+          <t>6,99; 21,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,57; 20,96</t>
+          <t>7,03; 22,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,33; 25,38</t>
+          <t>8,82; 24,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,99; 12,25</t>
+          <t>1,01; 11,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,58; 18,16</t>
+          <t>7,92; 18,09</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,57; 16,73</t>
+          <t>6,53; 16,83</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,69; 21,88</t>
+          <t>11,03; 22,11</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,95; 8,81</t>
+          <t>1,87; 8,37</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,14; 15,77</t>
+          <t>6,02; 15,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,59; 17,4</t>
+          <t>7,09; 17,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,46; 15,48</t>
+          <t>5,56; 14,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,25; 12,73</t>
+          <t>3,15; 12,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,32; 9,57</t>
+          <t>2,44; 9,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,94; 18,05</t>
+          <t>8,0; 19,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,78; 11,69</t>
+          <t>4,17; 12,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,03; 11,2</t>
+          <t>2,96; 11,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,25; 11,1</t>
+          <t>5,09; 10,89</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,05; 16,42</t>
+          <t>9,0; 16,15</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,55; 11,77</t>
+          <t>5,71; 11,8</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,22; 10,16</t>
+          <t>3,97; 10,13</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 10,39</t>
+          <t>1,18; 12,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,24; 19,12</t>
+          <t>6,26; 19,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 9,0</t>
+          <t>0,97; 8,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,64; 19,41</t>
+          <t>5,74; 18,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,76; 9,41</t>
+          <t>1,74; 9,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,11; 17,38</t>
+          <t>4,93; 17,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,78</t>
+          <t>0,0; 5,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,89; 16,11</t>
+          <t>3,93; 16,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 7,7</t>
+          <t>1,97; 7,61</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,5; 16,55</t>
+          <t>6,99; 16,0</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 5,34</t>
+          <t>1,02; 5,71</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,83; 14,7</t>
+          <t>5,99; 14,94</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,24; 14,71</t>
+          <t>4,54; 15,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,89; 17,74</t>
+          <t>6,28; 18,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,68; 21,28</t>
+          <t>7,89; 20,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,18; 12,61</t>
+          <t>2,06; 12,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,73; 16,12</t>
+          <t>5,65; 17,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,16; 14,03</t>
+          <t>3,64; 14,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,12; 20,27</t>
+          <t>7,47; 20,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,12; 20,15</t>
+          <t>2,44; 19,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,98; 14,08</t>
+          <t>6,42; 13,8</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,73; 13,76</t>
+          <t>6,06; 13,81</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,46; 17,63</t>
+          <t>8,74; 17,51</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,63; 14,17</t>
+          <t>3,93; 13,88</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,91</t>
+          <t>0,0; 11,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,38; 30,61</t>
+          <t>10,41; 31,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,49; 19,85</t>
+          <t>4,26; 19,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,19; 19,85</t>
+          <t>4,38; 18,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,52</t>
+          <t>0,0; 7,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,22; 23,55</t>
+          <t>6,85; 22,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,18; 10,57</t>
+          <t>1,17; 9,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,55; 14,44</t>
+          <t>2,62; 16,13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 6,28</t>
+          <t>0,71; 5,72</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10,07; 23,36</t>
+          <t>10,44; 23,49</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,48; 12,73</t>
+          <t>3,47; 11,62</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,55; 14,03</t>
+          <t>4,32; 14,38</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,47; 14,3</t>
+          <t>2,43; 13,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,95; 17,56</t>
+          <t>3,93; 17,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,2</t>
+          <t>0,0; 7,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,14; 16,99</t>
+          <t>4,02; 17,81</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,06; 11,52</t>
+          <t>1,99; 10,75</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,59; 15,27</t>
+          <t>3,54; 16,66</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,06</t>
+          <t>0,0; 10,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11,32; 27,49</t>
+          <t>10,45; 27,24</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,72; 9,84</t>
+          <t>2,88; 10,05</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,82; 13,58</t>
+          <t>5,6; 14,42</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,64; 6,03</t>
+          <t>0,65; 6,22</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,21; 19,99</t>
+          <t>9,29; 19,98</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,3; 11,17</t>
+          <t>3,16; 10,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,5; 8,74</t>
+          <t>2,46; 8,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,09; 7,87</t>
+          <t>1,91; 7,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,26; 14,63</t>
+          <t>5,86; 14,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,01; 6,32</t>
+          <t>1,43; 6,04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,86; 7,67</t>
+          <t>1,74; 7,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,43; 6,59</t>
+          <t>1,42; 6,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,41; 14,47</t>
+          <t>5,36; 14,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,58; 6,81</t>
+          <t>2,58; 6,74</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,85; 7,2</t>
+          <t>2,74; 7,08</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,35; 6,24</t>
+          <t>2,39; 6,27</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,42; 12,54</t>
+          <t>6,72; 12,96</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,9; 6,46</t>
+          <t>1,58; 6,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,0; 7,2</t>
+          <t>2,22; 7,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,38; 12,07</t>
+          <t>5,44; 12,27</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,48; 6,09</t>
+          <t>1,48; 5,94</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,63; 12,6</t>
+          <t>5,72; 13,15</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,37; 9,48</t>
+          <t>3,7; 9,83</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,46; 9,39</t>
+          <t>3,82; 9,63</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,04; 9,42</t>
+          <t>3,09; 9,47</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,44; 8,81</t>
+          <t>4,47; 8,76</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3,42; 7,37</t>
+          <t>3,47; 7,67</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5,26; 9,53</t>
+          <t>5,17; 9,42</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,8; 6,78</t>
+          <t>2,79; 6,85</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,03; 8,08</t>
+          <t>5,05; 8,16</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,05; 10,49</t>
+          <t>6,95; 10,52</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,33; 9,62</t>
+          <t>6,34; 9,67</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,41; 8,92</t>
+          <t>5,56; 8,8</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,26; 8,01</t>
+          <t>5,19; 8,12</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,8; 10,13</t>
+          <t>7,0; 10,27</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,21; 8,19</t>
+          <t>5,14; 8,1</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,25; 9,82</t>
+          <t>6,02; 9,55</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,45; 7,64</t>
+          <t>5,58; 7,65</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7,37; 9,91</t>
+          <t>7,37; 9,86</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6,23; 8,39</t>
+          <t>6,15; 8,38</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6,28; 8,91</t>
+          <t>6,31; 8,82</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolores o síntomas (tasa de respuesta: 99,99%)</t>
+          <t>Menores que en las últimas 2 semanas limitaron su actividad por dolores o síntomas (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2713; 9904</t>
+          <t>2715; 10085</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2135; 9882</t>
+          <t>1922; 9950</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5168; 14285</t>
+          <t>5081; 14252</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>870; 7206</t>
+          <t>1263; 8262</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4732; 13225</t>
+          <t>4210; 13229</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4255; 13586</t>
+          <t>4554; 14303</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6017; 16362</t>
+          <t>5687; 15628</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>786; 9721</t>
+          <t>802; 8933</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8545; 20484</t>
+          <t>8935; 20401</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8031; 20456</t>
+          <t>7983; 20567</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13021; 26656</t>
+          <t>13437; 26936</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2983; 13450</t>
+          <t>2859; 12782</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6239; 16019</t>
+          <t>6112; 15442</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7943; 18220</t>
+          <t>7429; 18235</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5673; 16092</t>
+          <t>5781; 15341</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4126; 16152</t>
+          <t>3990; 15768</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2522; 10407</t>
+          <t>2652; 9947</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8830; 20063</t>
+          <t>8891; 21687</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4171; 12891</t>
+          <t>4593; 13816</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3868; 14286</t>
+          <t>3774; 14061</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11042; 23336</t>
+          <t>10712; 22895</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19542; 35446</t>
+          <t>19430; 34860</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11884; 25205</t>
+          <t>12228; 25278</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10728; 25849</t>
+          <t>10097; 25785</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>779; 7023</t>
+          <t>799; 8279</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4255; 13035</t>
+          <t>4266; 13613</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>662; 6017</t>
+          <t>648; 5536</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3284; 11310</t>
+          <t>3343; 10881</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1238; 6615</t>
+          <t>1227; 6889</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3643; 12384</t>
+          <t>3516; 12551</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4742</t>
+          <t>0; 4127</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2611; 10817</t>
+          <t>2641; 11320</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2656; 10615</t>
+          <t>2714; 10500</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10453; 23074</t>
+          <t>9743; 22307</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1326; 7296</t>
+          <t>1398; 7808</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7314; 18437</t>
+          <t>7513; 18735</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3171; 11013</t>
+          <t>3399; 11412</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4581; 13792</t>
+          <t>4886; 14302</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5910; 16376</t>
+          <t>6076; 16107</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1529; 8844</t>
+          <t>1447; 8623</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4533; 12755</t>
+          <t>4468; 14029</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2598; 11539</t>
+          <t>2995; 11663</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5784; 16455</t>
+          <t>6064; 16547</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2439; 15743</t>
+          <t>1905; 14862</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9205; 21681</t>
+          <t>9891; 21252</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9168; 22014</t>
+          <t>9699; 22101</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13384; 27874</t>
+          <t>13825; 27697</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5382; 21014</t>
+          <t>5828; 20583</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4147</t>
+          <t>0; 4649</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4557; 13437</t>
+          <t>4571; 13684</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1952; 8623</t>
+          <t>1852; 8419</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1447; 6851</t>
+          <t>1513; 6509</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3370</t>
+          <t>0; 3369</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3374; 11009</t>
+          <t>3202; 10746</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>549; 4898</t>
+          <t>544; 4570</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1036; 5879</t>
+          <t>1066; 6566</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>625; 5444</t>
+          <t>619; 4959</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9126; 21176</t>
+          <t>9464; 21294</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3126; 11434</t>
+          <t>3118; 10432</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3425; 10553</t>
+          <t>3248; 10816</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1386; 8016</t>
+          <t>1361; 7420</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2210; 9832</t>
+          <t>2201; 9639</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3906</t>
+          <t>0; 4309</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1914; 7844</t>
+          <t>1855; 8222</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1232; 6880</t>
+          <t>1191; 6419</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2161; 9197</t>
+          <t>2135; 10038</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 6964</t>
+          <t>0; 6059</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6358; 15445</t>
+          <t>5873; 15303</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3149; 11394</t>
+          <t>3337; 11637</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5600; 15783</t>
+          <t>6509; 16758</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>717; 6752</t>
+          <t>724; 6964</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9426; 20461</t>
+          <t>9505; 20449</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4243; 14362</t>
+          <t>4066; 12936</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3462; 12117</t>
+          <t>3410; 11993</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2866; 10814</t>
+          <t>2619; 10467</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7796; 18221</t>
+          <t>7296; 17918</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1375; 8567</t>
+          <t>1935; 8195</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2707; 11179</t>
+          <t>2535; 11226</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2066; 9488</t>
+          <t>2042; 10073</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>8435; 22569</t>
+          <t>8357; 22219</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6825; 17992</t>
+          <t>6829; 17802</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8112; 20477</t>
+          <t>7800; 20148</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6602; 17552</t>
+          <t>6732; 17640</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>18018; 35173</t>
+          <t>18850; 36351</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2995; 10200</t>
+          <t>2502; 10162</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3301; 11864</t>
+          <t>3651; 11852</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8797; 19736</t>
+          <t>8899; 20077</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1950; 8018</t>
+          <t>1949; 7816</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>9237; 20667</t>
+          <t>9385; 21578</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5771; 16247</t>
+          <t>6334; 16847</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5911; 16037</t>
+          <t>6530; 16450</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>4772; 14765</t>
+          <t>4839; 14842</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>14282; 28356</t>
+          <t>14394; 28197</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>11485; 24764</t>
+          <t>11657; 25777</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>17603; 31871</t>
+          <t>17284; 31507</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>8087; 19568</t>
+          <t>8037; 19755</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>34289; 55048</t>
+          <t>34365; 55556</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>50187; 74651</t>
+          <t>49428; 74848</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>44576; 67704</t>
+          <t>44619; 68026</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>35978; 59317</t>
+          <t>37016; 58539</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>38030; 57921</t>
+          <t>37521; 58690</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>51223; 76314</t>
+          <t>52770; 77354</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>38826; 61026</t>
+          <t>38294; 60359</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>47607; 74856</t>
+          <t>45885; 72733</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>76515; 107244</t>
+          <t>78269; 107397</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>107969; 145150</t>
+          <t>107955; 144490</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>90269; 121541</t>
+          <t>89092; 121457</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>89665; 127135</t>
+          <t>90023; 125932</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>13,11%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12,69%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>15,72%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4,16%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>10,89%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>8,61%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>15,98%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4,6%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>13,11%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>12,69%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15,72%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,16; 19,18</t>
+          <t>7,19; 21,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,35; 17,33</t>
+          <t>6,56; 20,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,86; 24,84</t>
+          <t>9,39; 25,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,72; 11,27</t>
+          <t>1,1; 11,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,99; 21,97</t>
+          <t>5,41; 18,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,03; 22,07</t>
+          <t>3,61; 17,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,82; 24,24</t>
+          <t>9,37; 24,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 11,26</t>
+          <t>2,03; 11,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,92; 18,09</t>
+          <t>7,72; 17,92</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,53; 16,83</t>
+          <t>6,48; 16,5</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,03; 22,11</t>
+          <t>11,15; 22,36</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,87; 8,37</t>
+          <t>2,35; 9,74</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5,35%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12,51%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7,26%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5,91%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>10,15%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>11,59%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>9,44%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7,5%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,35%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>12,51%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>7,26%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,02; 15,2</t>
+          <t>2,81; 9,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,09; 17,41</t>
+          <t>8,43; 18,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,56; 14,76</t>
+          <t>3,74; 11,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,15; 12,43</t>
+          <t>3,07; 10,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,44; 9,15</t>
+          <t>6,03; 15,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,0; 19,51</t>
+          <t>7,15; 17,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,17; 12,53</t>
+          <t>5,04; 14,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,96; 11,02</t>
+          <t>5,56; 16,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,09; 10,89</t>
+          <t>5,04; 11,04</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,0; 16,15</t>
+          <t>8,64; 15,8</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,71; 11,8</t>
+          <t>5,55; 11,79</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,97; 10,13</t>
+          <t>5,02; 11,83</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4,46%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10,22%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8,51%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>4,47%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>11,77%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>3,22%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>11,02%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4,46%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>10,22%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,18; 12,25</t>
+          <t>1,78; 9,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,26; 19,97</t>
+          <t>5,13; 17,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 8,28</t>
+          <t>0,0; 5,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,74; 18,67</t>
+          <t>3,88; 16,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,74; 9,8</t>
+          <t>1,13; 11,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,93; 17,61</t>
+          <t>6,33; 19,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,9</t>
+          <t>0,97; 8,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,93; 16,86</t>
+          <t>5,11; 18,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 7,61</t>
+          <t>2,05; 7,63</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,99; 16,0</t>
+          <t>7,07; 16,25</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 5,71</t>
+          <t>0,97; 5,72</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,99; 14,94</t>
+          <t>5,58; 14,12</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10,33%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7,72%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12,7%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9,3%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>8,62%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>10,98%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>12,79%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5,82%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10,33%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,72%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12,7%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,54; 15,24</t>
+          <t>5,75; 17,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,28; 18,39</t>
+          <t>3,28; 13,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,89; 20,93</t>
+          <t>7,09; 19,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,06; 12,29</t>
+          <t>2,56; 21,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,65; 17,73</t>
+          <t>4,66; 14,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,64; 14,18</t>
+          <t>6,27; 18,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,47; 20,38</t>
+          <t>7,87; 20,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,44; 19,02</t>
+          <t>2,44; 14,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,42; 13,8</t>
+          <t>6,15; 13,76</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,06; 13,81</t>
+          <t>6,03; 14,31</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,74; 17,51</t>
+          <t>8,5; 17,68</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,93; 13,88</t>
+          <t>3,76; 14,41</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>13,62%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3,85%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>3,18%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>19,11%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>10,39%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>10,18%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>13,62%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>3,85%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,11</t>
+          <t>0,0; 7,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,41; 31,17</t>
+          <t>6,87; 23,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,26; 19,38</t>
+          <t>1,2; 11,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,38; 18,86</t>
+          <t>2,75; 15,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,51</t>
+          <t>0,0; 9,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,85; 22,98</t>
+          <t>10,85; 31,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,17; 9,86</t>
+          <t>4,85; 20,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,62; 16,13</t>
+          <t>4,22; 19,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,71; 5,72</t>
+          <t>0,72; 6,31</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10,44; 23,49</t>
+          <t>10,48; 23,7</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,47; 11,62</t>
+          <t>3,46; 12,2</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,32; 14,38</t>
+          <t>4,65; 14,6</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5,16%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8,36%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3,06%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>17,73%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>6,53%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>9,33%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>1,34%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>8,96%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>5,16%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>8,36%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3,06%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,43; 13,24</t>
+          <t>2,04; 11,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,93; 17,22</t>
+          <t>3,56; 16,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,94</t>
+          <t>0,0; 10,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,02; 17,81</t>
+          <t>10,87; 27,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,99; 10,75</t>
+          <t>2,48; 14,2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,54; 16,66</t>
+          <t>3,88; 17,71</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,49</t>
+          <t>0,0; 6,22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,45; 27,24</t>
+          <t>3,88; 17,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,88; 10,05</t>
+          <t>3,07; 10,22</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,6; 14,42</t>
+          <t>5,06; 14,25</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,65; 6,22</t>
+          <t>0,65; 6,18</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,29; 19,98</t>
+          <t>8,99; 18,9</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2,98%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4,14%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>9,84%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>5,89%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>5,16%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>4,33%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>9,83%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,14%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,36%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,16; 10,06</t>
+          <t>1,01; 6,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,46; 8,65</t>
+          <t>1,87; 8,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,91; 7,62</t>
+          <t>1,48; 6,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,86; 14,39</t>
+          <t>5,71; 15,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,43; 6,04</t>
+          <t>3,17; 10,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,74; 7,7</t>
+          <t>2,57; 9,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,42; 6,99</t>
+          <t>2,11; 8,0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,36; 14,24</t>
+          <t>6,39; 15,32</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,58; 6,74</t>
+          <t>2,81; 6,91</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,74; 7,08</t>
+          <t>2,84; 7,12</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,39; 6,27</t>
+          <t>2,31; 6,27</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,72; 12,96</t>
+          <t>6,96; 13,85</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>8,89%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>6,04%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>6,02%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>5,48%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>3,67%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>4,18%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>8,29%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>3,03%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>8,89%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>6,04%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>6,02%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,58; 6,44</t>
+          <t>5,78; 12,76</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,22; 7,2</t>
+          <t>3,44; 9,83</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,44; 12,27</t>
+          <t>3,39; 9,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,48; 5,94</t>
+          <t>2,85; 9,33</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,72; 13,15</t>
+          <t>1,79; 6,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,7; 9,83</t>
+          <t>2,25; 6,95</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,82; 9,63</t>
+          <t>5,35; 12,43</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,09; 9,47</t>
+          <t>1,1; 5,09</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,47; 8,76</t>
+          <t>4,22; 8,42</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3,47; 7,67</t>
+          <t>3,47; 7,46</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5,17; 9,42</t>
+          <t>5,15; 9,69</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,79; 6,85</t>
+          <t>2,42; 6,3</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>6,56%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>8,44%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>6,51%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>7,91%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>6,44%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>8,62%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>7,92%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>7,1%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>6,56%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>8,44%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>6,51%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,05; 8,16</t>
+          <t>5,14; 8,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,95; 10,52</t>
+          <t>6,82; 10,27</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,34; 9,67</t>
+          <t>5,06; 8,05</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,56; 8,8</t>
+          <t>6,23; 10,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,19; 8,12</t>
+          <t>5,04; 8,15</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,0; 10,27</t>
+          <t>7,04; 10,37</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,14; 8,1</t>
+          <t>6,25; 9,63</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,02; 9,55</t>
+          <t>5,78; 9,39</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,58; 7,65</t>
+          <t>5,44; 7,59</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7,37; 9,86</t>
+          <t>7,47; 10,0</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6,15; 8,38</t>
+          <t>6,07; 8,36</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6,31; 8,82</t>
+          <t>6,47; 9,05</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>7892</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8227</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10136</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2669</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>5727</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>4945</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>9167</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3374</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>7892</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>8227</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>10136</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6555</t>
+          <t>5703</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2715; 10085</t>
+          <t>4331; 12906</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1922; 9950</t>
+          <t>4254; 13535</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5081; 14252</t>
+          <t>6052; 16253</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1263; 8262</t>
+          <t>704; 7165</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4210; 13229</t>
+          <t>2846; 9901</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4554; 14303</t>
+          <t>2072; 10220</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5687; 15628</t>
+          <t>5375; 14234</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>802; 8933</t>
+          <t>1144; 6445</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8935; 20401</t>
+          <t>8704; 20215</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7983; 20567</t>
+          <t>7921; 20168</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13437; 26936</t>
+          <t>13589; 27247</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2859; 12782</t>
+          <t>2831; 11752</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5820</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>13906</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8007</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6851</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>10308</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>12138</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>9816</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9519</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5820</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>13906</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>8007</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7782</t>
+          <t>9761</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17301</t>
+          <t>16613</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6112; 15442</t>
+          <t>3056; 10331</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7429; 18235</t>
+          <t>9367; 20641</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5781; 15341</t>
+          <t>4123; 13149</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3990; 15768</t>
+          <t>3552; 12194</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2652; 9947</t>
+          <t>6123; 15578</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8891; 21687</t>
+          <t>7491; 17884</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4593; 13816</t>
+          <t>5242; 15238</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3774; 14061</t>
+          <t>5589; 16286</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10712; 22895</t>
+          <t>10601; 23213</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19430; 34860</t>
+          <t>18643; 34104</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12228; 25278</t>
+          <t>11892; 25266</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10097; 25785</t>
+          <t>10853; 25592</t>
         </is>
       </c>
     </row>
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>3138</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7280</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1355</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5050</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>3022</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>8022</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>2149</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6421</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>3138</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>7280</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1355</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5768</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12189</t>
+          <t>11050</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>799; 8279</t>
+          <t>1249; 6913</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4266; 13613</t>
+          <t>3656; 12633</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>648; 5536</t>
+          <t>0; 4070</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3343; 10881</t>
+          <t>2305; 9531</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1227; 6889</t>
+          <t>766; 7461</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3516; 12551</t>
+          <t>4318; 13134</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4127</t>
+          <t>649; 5844</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2641; 11320</t>
+          <t>2890; 10519</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2714; 10500</t>
+          <t>2827; 10520</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9743; 22307</t>
+          <t>9858; 22663</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1398; 7808</t>
+          <t>1332; 7822</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7513; 18735</t>
+          <t>6464; 16365</t>
         </is>
       </c>
     </row>
@@ -2697,32 +2697,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>8172</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6352</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6708</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>6451</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>8537</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>9842</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4084</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>8172</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>6352</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>10307</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6845</t>
+          <t>4433</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10929</t>
+          <t>11141</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3399; 11412</t>
+          <t>4548; 13528</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4886; 14302</t>
+          <t>2700; 11396</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6076; 16107</t>
+          <t>5755; 15986</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1447; 8623</t>
+          <t>1850; 15437</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4468; 14029</t>
+          <t>3492; 10903</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2995; 11663</t>
+          <t>4875; 14086</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6064; 16547</t>
+          <t>6055; 15429</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1905; 14862</t>
+          <t>1727; 10013</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9891; 21252</t>
+          <t>9473; 21185</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9699; 22101</t>
+          <t>9640; 22899</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13825; 27697</t>
+          <t>13444; 27968</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5828; 20583</t>
+          <t>5375; 20603</t>
         </is>
       </c>
     </row>
@@ -2905,42 +2905,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>6369</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1784</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2809</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>1333</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>8390</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>4511</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>3514</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>6369</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>1784</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>3633</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6319</t>
+          <t>6442</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4649</t>
+          <t>0; 3361</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4571; 13684</t>
+          <t>3212; 10963</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1852; 8419</t>
+          <t>554; 5390</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1513; 6509</t>
+          <t>1087; 6255</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3369</t>
+          <t>0; 4157</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3202; 10746</t>
+          <t>4764; 13643</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>544; 4570</t>
+          <t>2108; 8930</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1066; 6566</t>
+          <t>1504; 6842</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>619; 4959</t>
+          <t>620; 5469</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9464; 21294</t>
+          <t>9503; 21488</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3118; 10432</t>
+          <t>3108; 10951</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3248; 10816</t>
+          <t>3493; 10980</t>
         </is>
       </c>
     </row>
@@ -3123,32 +3123,32 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>3082</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>5035</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1766</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>8678</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>3662</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>5222</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>729</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4136</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>3082</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>5035</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1766</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>10042</t>
+          <t>4084</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>14179</t>
+          <t>12762</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1361; 7420</t>
+          <t>1218; 6746</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2201; 9639</t>
+          <t>2142; 9749</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4309</t>
+          <t>0; 6282</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1855; 8222</t>
+          <t>5320; 13516</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1191; 6419</t>
+          <t>1389; 7961</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2135; 10038</t>
+          <t>2170; 9915</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 6059</t>
+          <t>0; 3378</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5873; 15303</t>
+          <t>1775; 7939</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3337; 11637</t>
+          <t>3552; 11838</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6509; 16758</t>
+          <t>5877; 16566</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>724; 6964</t>
+          <t>723; 6920</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9505; 20449</t>
+          <t>8512; 17899</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>4044</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>6040</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>4847</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>13908</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>7572</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>7158</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>5951</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>12233</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>4044</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>6040</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>4847</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>13925</t>
+          <t>12244</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>26159</t>
+          <t>26152</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4066; 12936</t>
+          <t>1369; 8762</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3410; 11993</t>
+          <t>2720; 11813</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2619; 10467</t>
+          <t>2126; 9230</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7296; 17918</t>
+          <t>8077; 21669</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1935; 8195</t>
+          <t>4071; 13170</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2535; 11226</t>
+          <t>3568; 12728</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2042; 10073</t>
+          <t>2892; 10993</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>8357; 22219</t>
+          <t>7831; 18769</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6829; 17802</t>
+          <t>7426; 18274</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7800; 20148</t>
+          <t>8090; 20267</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6732; 17640</t>
+          <t>6511; 17636</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>18850; 36351</t>
+          <t>18356; 36548</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>14579</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>10352</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>10280</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>8730</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>5803</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>6881</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>13561</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>3990</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>14579</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>10352</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>10280</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>8755</t>
+          <t>3460</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>12745</t>
+          <t>12189</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2502; 10162</t>
+          <t>9481; 20929</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3651; 11852</t>
+          <t>5887; 16842</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8899; 20077</t>
+          <t>5798; 16075</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1949; 7816</t>
+          <t>4543; 14880</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>9385; 21578</t>
+          <t>2825; 10260</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>6334; 16847</t>
+          <t>3710; 11445</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6530; 16450</t>
+          <t>8750; 20327</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>4839; 14842</t>
+          <t>1540; 7150</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>14394; 28197</t>
+          <t>13572; 27108</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>11657; 25777</t>
+          <t>11649; 25060</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>17284; 31507</t>
+          <t>17238; 32394</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>8037; 19755</t>
+          <t>7272; 18896</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>77</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>47392</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>63560</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>48482</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>55404</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>43878</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>61292</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>55726</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>47272</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>47392</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>63560</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>48482</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>59103</t>
+          <t>46649</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>106375</t>
+          <t>102053</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>34365; 55556</t>
+          <t>37145; 58298</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>49428; 74848</t>
+          <t>51375; 77387</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>44619; 68026</t>
+          <t>37665; 59976</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>37016; 58539</t>
+          <t>43666; 70112</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>37521; 58690</t>
+          <t>34308; 55512</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>52770; 77354</t>
+          <t>50093; 73802</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>38294; 60359</t>
+          <t>43970; 67739</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>45885; 72733</t>
+          <t>36345; 59025</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>78269; 107397</t>
+          <t>76421; 106506</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>107955; 144490</t>
+          <t>109361; 146480</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>89092; 121457</t>
+          <t>87932; 121156</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>90023; 125932</t>
+          <t>85971; 120273</t>
         </is>
       </c>
     </row>
